--- a/partner_results/imr/ClassMissingCurationStatus_imr.xlsx
+++ b/partner_results/imr/ClassMissingCurationStatus_imr.xlsx
@@ -455,22 +455,30 @@
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>distance between sensor and extrudate [imr]</t>
+          <t>surface of extrudate [imr]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>relational quality</t>
+          <t>surface layer (fiat object part)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>uppermost layer of the extrudate</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -496,19 +504,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>extrudate norm [imr]</t>
+          <t>distance between sensor and extrudate [imr]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>relational quality</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ideal dimensions and shape of the
-extrudate defined by the manufacturer</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -516,18 +523,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>surface of extrudate [imr]</t>
+          <t>extrudate norm [imr]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>surface layer (fiat object part)</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>uppermost layer of the extrudate</t>
+          <t>ideal dimensions and shape of the
+extrudate defined by the manufacturer</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
